--- a/StructureDefinition-lmdi-bundle.xlsx
+++ b/StructureDefinition-lmdi-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:35:49+00:00</t>
+    <t>2026-03-10T12:49:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-lmdi-bundle.xlsx
+++ b/StructureDefinition-lmdi-bundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.7</t>
+    <t>1.0.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T12:49:22+00:00</t>
+    <t>2026-03-10T15:33:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,15 +269,16 @@
   </si>
   <si>
     <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}lr-allowed-resources:Bundle kan bare inneholde følgende profilerte ressurstyper: Diagnose, Helsepersonell, Episode, Legemiddel, LegemiddelAdministrasjon, Legemiddelrekvirering, Organisasjon, Pasient {entry.all(
-  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-condition').exists() or 
-  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-practitioner').exists() or 
-  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-encounter').exists() or 
-  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-medication').exists() or 
-  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-medicationadministration').exists() or 
-  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-medicationrequest').exists() or 
-  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-organization').exists() or 
-  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-patient').exists()
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}lr-allowed-resources:Bundle kan bare inneholde følgende profilerte ressurstyper: Diagnose, Helsepersonell, Episode, Legemiddel, LegemiddelAdministrasjon, Legemiddelrekvirering, Organisasjon, Pasient, Virkestoff {entry.all(
+  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-condition').exists() or
+  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-practitioner').exists() or
+  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-encounter').exists() or
+  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-medication').exists() or
+  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-medicationadministration').exists() or
+  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-medicationrequest').exists() or
+  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-organization').exists() or
+  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-patient').exists() or
+  resource.meta.profile.where($this = 'http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-substance').exists()
 )}</t>
   </si>
   <si>
@@ -741,7 +742,7 @@
     <t>URL for requesten (påkrevd, men verdien har ingen betydning)</t>
   </si>
   <si>
-    <t>Representerer addressen for requesten. URL er påkrevd av FHIR-spesifikasjonen for transaction bundles, men selve verdien har ingen funksjonell betydning i dette tilfellet.</t>
+    <t>Representerer adressen for requesten. URL er påkrevd av FHIR-spesifikasjonen for transaction bundles, men selve verdien har ingen funksjonell betydning i dette tilfellet.</t>
   </si>
   <si>
     <t>E.g. for a Patient Create, the method would be "POST" and the URL would be "Patient". For a Patient Update, the method would be PUT and the URL would be "Patient/[id]".</t>

--- a/StructureDefinition-lmdi-bundle.xlsx
+++ b/StructureDefinition-lmdi-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T15:33:20+00:00</t>
+    <t>2026-03-18T15:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-lmdi-bundle.xlsx
+++ b/StructureDefinition-lmdi-bundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T15:02:12+00:00</t>
+    <t>2026-04-21T11:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-lmdi-bundle.xlsx
+++ b/StructureDefinition-lmdi-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T07:26:56+00:00</t>
+    <t>2026-05-11T08:19:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-lmdi-bundle.xlsx
+++ b/StructureDefinition-lmdi-bundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T08:19:23+00:00</t>
+    <t>2026-05-31T19:08:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-lmdi-bundle.xlsx
+++ b/StructureDefinition-lmdi-bundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-31T19:08:08+00:00</t>
+    <t>2026-06-12T10:49:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-lmdi-bundle.xlsx
+++ b/StructureDefinition-lmdi-bundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T10:49:58+00:00</t>
+    <t>2026-08-24T07:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
